--- a/results/02_taxa_assemblage/MRT_Method/ModelA_CoreOnly/tables/site_eval_heldout.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelA_CoreOnly/tables/site_eval_heldout.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,20 +486,15 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Prob_Cluster 3</t>
+          <t>p_max</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>p_max</t>
+          <t>delta_p</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>delta_p</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
@@ -508,7 +503,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>016C</t>
+          <t>011A</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -520,39 +515,36 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>1.524</v>
+        <v>6.2484</v>
       </c>
       <c r="F2" t="n">
-        <v>7.54</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>19.66</v>
+        <v>21.96</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8723404255319149</v>
+        <v>1.580246913580247</v>
       </c>
       <c r="I2" t="n">
-        <v>0.87</v>
+        <v>1.57</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.9375</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.0625</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5</v>
+        <v>0.9375</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="O2" t="inlineStr">
+        <v>0.875</v>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>Held-out</t>
         </is>
@@ -561,11 +553,11 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>033ABC</t>
+          <t>016C</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -573,39 +565,36 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>9.144</v>
+        <v>1.524</v>
       </c>
       <c r="F3" t="n">
-        <v>6.55</v>
+        <v>7.54</v>
       </c>
       <c r="G3" t="n">
-        <v>19.13</v>
+        <v>19.66</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1</v>
+        <v>0.8723404255319149</v>
       </c>
       <c r="I3" t="n">
-        <v>1.45</v>
+        <v>0.87</v>
       </c>
       <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
       </c>
-      <c r="N3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Held-out</t>
         </is>
@@ -614,11 +603,11 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>109C</t>
+          <t>026C</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -626,39 +615,36 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>3.048</v>
+        <v>8.9916</v>
       </c>
       <c r="F4" t="n">
-        <v>8.119999999999999</v>
+        <v>6.88</v>
       </c>
       <c r="G4" t="n">
-        <v>19.5</v>
+        <v>19.68</v>
       </c>
       <c r="H4" t="n">
-        <v>1.05</v>
+        <v>0.3125</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1</v>
+        <v>1.795</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3571428571428572</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1428571428571428</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="O4" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>Held-out</t>
         </is>
@@ -667,7 +653,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>121C</t>
+          <t>033ABC</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -675,43 +661,40 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9624</v>
+        <v>9.144</v>
       </c>
       <c r="F5" t="n">
-        <v>5.75</v>
+        <v>6.55</v>
       </c>
       <c r="G5" t="n">
-        <v>17.11</v>
+        <v>19.13</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7096774193548387</v>
+        <v>1.1</v>
       </c>
       <c r="I5" t="n">
-        <v>2.47</v>
+        <v>1.45</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.9375</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.0625</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5</v>
+        <v>0.9375</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="O5" t="inlineStr">
+        <v>0.875</v>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>Held-out</t>
         </is>
@@ -720,7 +703,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>122B</t>
+          <t>064B</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -732,39 +715,36 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>1.43256</v>
+        <v>1.524</v>
       </c>
       <c r="F6" t="n">
-        <v>9.52</v>
+        <v>10.31</v>
       </c>
       <c r="G6" t="n">
-        <v>17.02</v>
+        <v>21.97</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5365853658536586</v>
+        <v>1.787878787878788</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5600000000000001</v>
+        <v>7.11</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.9375</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.0625</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5</v>
+        <v>0.9375</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="O6" t="inlineStr">
+        <v>0.875</v>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>Held-out</t>
         </is>
@@ -773,7 +753,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>133B</t>
+          <t>066A</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -781,43 +761,40 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8288</v>
+        <v>1.3716</v>
       </c>
       <c r="F7" t="n">
-        <v>11.76</v>
+        <v>10.76</v>
       </c>
       <c r="G7" t="n">
-        <v>20.62</v>
+        <v>22.46</v>
       </c>
       <c r="H7" t="n">
-        <v>1.023255813953488</v>
+        <v>1.769230769230769</v>
       </c>
       <c r="I7" t="n">
-        <v>1.55</v>
+        <v>3.61</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.9375</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.0625</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5</v>
+        <v>0.9375</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="O7" t="inlineStr">
+        <v>0.875</v>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>Held-out</t>
         </is>
@@ -826,51 +803,48 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>073C</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>4.6</v>
+        <v>7.62</v>
       </c>
       <c r="F8" t="n">
-        <v>10.03</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>20.77</v>
+        <v>20.68</v>
       </c>
       <c r="H8" t="n">
-        <v>1.433404487688642</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="I8" t="n">
-        <v>0.41342143147169</v>
+        <v>1.12</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3571428571428572</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1428571428571428</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="O8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>Held-out</t>
         </is>
@@ -879,11 +853,11 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>109C</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -891,39 +865,36 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>1.5</v>
+        <v>3.048</v>
       </c>
       <c r="F9" t="n">
-        <v>10.12</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>19.12</v>
+        <v>19.5</v>
       </c>
       <c r="H9" t="n">
-        <v>1.541641360461585</v>
+        <v>1.05</v>
       </c>
       <c r="I9" t="n">
-        <v>1.08693561108866</v>
+        <v>1.1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.9375</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.0625</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5</v>
+        <v>0.9375</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="O9" t="inlineStr">
+        <v>0.875</v>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>Held-out</t>
         </is>
@@ -932,7 +903,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>121C</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -940,43 +911,40 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>3.9624</v>
       </c>
       <c r="F10" t="n">
-        <v>10.4</v>
+        <v>5.75</v>
       </c>
       <c r="G10" t="n">
-        <v>19.57</v>
+        <v>17.11</v>
       </c>
       <c r="H10" t="n">
-        <v>1.62995516333357</v>
+        <v>0.7096774193548387</v>
       </c>
       <c r="I10" t="n">
-        <v>1.50490599353894</v>
+        <v>2.47</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O10" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>Held-out</t>
         </is>
@@ -985,7 +953,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>122B</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -997,39 +965,36 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8</v>
+        <v>1.43256</v>
       </c>
       <c r="F11" t="n">
-        <v>9.789999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="G11" t="n">
-        <v>19.2</v>
+        <v>17.02</v>
       </c>
       <c r="H11" t="n">
-        <v>1.698140741541455</v>
+        <v>0.5365853658536586</v>
       </c>
       <c r="I11" t="n">
-        <v>2.16766115621638</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O11" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>Held-out</t>
         </is>
@@ -1038,11 +1003,11 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>133B</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1050,39 +1015,36 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1</v>
+        <v>1.8288</v>
       </c>
       <c r="F12" t="n">
-        <v>10.12</v>
+        <v>11.76</v>
       </c>
       <c r="G12" t="n">
-        <v>17.91</v>
+        <v>20.62</v>
       </c>
       <c r="H12" t="n">
-        <v>1.699273096764108</v>
+        <v>1.023255813953488</v>
       </c>
       <c r="I12" t="n">
-        <v>1.05926908510679</v>
+        <v>1.55</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O12" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>Held-out</t>
         </is>
@@ -1091,7 +1053,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>139B</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1103,39 +1065,36 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6</v>
+        <v>1.3716</v>
       </c>
       <c r="F13" t="n">
-        <v>9.94</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>19.92</v>
+        <v>20.5</v>
       </c>
       <c r="H13" t="n">
-        <v>1.482019854132901</v>
+        <v>1.16</v>
       </c>
       <c r="I13" t="n">
-        <v>0.542826236601442</v>
+        <v>1.82</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.9375</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.0625</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5</v>
+        <v>0.9375</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="O13" t="inlineStr">
+        <v>0.875</v>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>Held-out</t>
         </is>
@@ -1144,51 +1103,48 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>GL1</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Uncertain</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="F14" t="n">
-        <v>9.32</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>22.45</v>
+        <v>26.89</v>
       </c>
       <c r="H14" t="n">
-        <v>1.525052642945845</v>
+        <v>1.611842946668372</v>
       </c>
       <c r="I14" t="n">
-        <v>0.511201323109319</v>
+        <v>1.07</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.9375</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0.0625</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>0.9375</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="inlineStr">
+        <v>0.875</v>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>Held-out</t>
         </is>
@@ -1197,7 +1153,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>S69</t>
+          <t>S18</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1209,39 +1165,36 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="F15" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="G15" t="n">
-        <v>22.89</v>
+        <v>19.57</v>
       </c>
       <c r="H15" t="n">
-        <v>1.860779140152104</v>
+        <v>1.62995516333357</v>
       </c>
       <c r="I15" t="n">
-        <v>1.84144213994961</v>
+        <v>1.50490599353894</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1</v>
+        <v>0.9375</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
       <c r="L15" t="n">
-        <v>0.9</v>
+        <v>0.9375</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O15" t="inlineStr">
+        <v>0.875</v>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>Held-out</t>
         </is>
@@ -1250,51 +1203,548 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
+          <t>S21</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Peripheral</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
+        <v>18.02</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.162022194821208</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.71138107667851</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Held-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>S28</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Peripheral</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="G17" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.542817329617431</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.84203344898835</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Held-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>S28(5)</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Peripheral</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>7</v>
+      </c>
+      <c r="G18" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.560047918538485</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Held-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>S51</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Peripheral</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F19" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="G19" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.482019854132901</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.542826236601442</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Held-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>S52</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Peripheral</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="G20" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.473299221677717</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.758892017654233</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Held-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>S53</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Peripheral</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="G21" t="n">
+        <v>22.45</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.525052642945845</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.511201323109319</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Held-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>S54</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="G22" t="n">
+        <v>21.15</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.520124887150165</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.601560297020399</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Held-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>S69</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Peripheral</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>22.89</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.860779140152104</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.84144213994961</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Held-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>S70</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Peripheral</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F24" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="G24" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.310133297964056</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.719020334793854</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Held-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>S72</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Peripheral</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F25" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="G25" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.3034886557697</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.07155989004254</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Held-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
           <t>S74</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Uncertain</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
+      <c r="B26" t="n">
         <v>3</v>
       </c>
-      <c r="E16" t="n">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Peripheral</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
         <v>4.9</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F26" t="n">
         <v>9.19</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G26" t="n">
         <v>20.65</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H26" t="n">
         <v>1.652212487523566</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I26" t="n">
         <v>1.50636152676643</v>
       </c>
-      <c r="J16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="J26" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>Held-out</t>
         </is>
